--- a/data.xlsx
+++ b/data.xlsx
@@ -1,36 +1,535 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mutual_Transfer Website\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB2CF85-7676-472B-B556-6BF4FBFAA475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stations" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Designations" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Departments" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Stations" sheetId="1" r:id="rId1"/>
+    <sheet name="Designations" sheetId="2" r:id="rId2"/>
+    <sheet name="Departments" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="161">
+  <si>
+    <t>Station</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>Mumbai</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>Kolkata</t>
+  </si>
+  <si>
+    <t>Hyderabad</t>
+  </si>
+  <si>
+    <t>Bengaluru</t>
+  </si>
+  <si>
+    <t>Pune</t>
+  </si>
+  <si>
+    <t>Ahmedabad</t>
+  </si>
+  <si>
+    <t>Lucknow</t>
+  </si>
+  <si>
+    <t>Jaipur</t>
+  </si>
+  <si>
+    <t>Designation</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Agartala</t>
+  </si>
+  <si>
+    <t>Agatti</t>
+  </si>
+  <si>
+    <t>Agra</t>
+  </si>
+  <si>
+    <t>Aizawl</t>
+  </si>
+  <si>
+    <t>Akola</t>
+  </si>
+  <si>
+    <t>Aligarh</t>
+  </si>
+  <si>
+    <t>Allahabad</t>
+  </si>
+  <si>
+    <t>Amritsar</t>
+  </si>
+  <si>
+    <t>Aurangabad</t>
+  </si>
+  <si>
+    <t>Ayodhya</t>
+  </si>
+  <si>
+    <t>Bagdogra</t>
+  </si>
+  <si>
+    <t>Balurghat</t>
+  </si>
+  <si>
+    <t>Bareilly</t>
+  </si>
+  <si>
+    <t>Bathinda</t>
+  </si>
+  <si>
+    <t>Belagavi</t>
+  </si>
+  <si>
+    <t>Berhampur</t>
+  </si>
+  <si>
+    <t>Bhavnagar</t>
+  </si>
+  <si>
+    <t>Bhopal</t>
+  </si>
+  <si>
+    <t>Bhubaneswar</t>
+  </si>
+  <si>
+    <t>Bhuj</t>
+  </si>
+  <si>
+    <t>Bikaner</t>
+  </si>
+  <si>
+    <t>Bilaspur</t>
+  </si>
+  <si>
+    <t>Chandigarh</t>
+  </si>
+  <si>
+    <t>Cochin</t>
+  </si>
+  <si>
+    <t>Coimbatore</t>
+  </si>
+  <si>
+    <t>Cooch Behar</t>
+  </si>
+  <si>
+    <t>Cuddapah</t>
+  </si>
+  <si>
+    <t>Daman</t>
+  </si>
+  <si>
+    <t>Daporijo</t>
+  </si>
+  <si>
+    <t>Darbhanga</t>
+  </si>
+  <si>
+    <t>Dehradun</t>
+  </si>
+  <si>
+    <t>Deoghar</t>
+  </si>
+  <si>
+    <t>Dhanbad</t>
+  </si>
+  <si>
+    <t>Dharamshala</t>
+  </si>
+  <si>
+    <t>Dibrugarh</t>
+  </si>
+  <si>
+    <t>Dimapur</t>
+  </si>
+  <si>
+    <t>Diu</t>
+  </si>
+  <si>
+    <t>Donakonda</t>
+  </si>
+  <si>
+    <t>Dubrajpur</t>
+  </si>
+  <si>
+    <t>Gaya</t>
+  </si>
+  <si>
+    <t>Goa</t>
+  </si>
+  <si>
+    <t>Gondia</t>
+  </si>
+  <si>
+    <t>Gorakhpur</t>
+  </si>
+  <si>
+    <t>Guwahati</t>
+  </si>
+  <si>
+    <t>Gwalior</t>
+  </si>
+  <si>
+    <t>Hissar</t>
+  </si>
+  <si>
+    <t>Hubballi</t>
+  </si>
+  <si>
+    <t>Imphal</t>
+  </si>
+  <si>
+    <t>Indore</t>
+  </si>
+  <si>
+    <t>Jabalpur</t>
+  </si>
+  <si>
+    <t>Jagdalpur</t>
+  </si>
+  <si>
+    <t>Jaisalmer</t>
+  </si>
+  <si>
+    <t>Jalgaon</t>
+  </si>
+  <si>
+    <t>Jammu</t>
+  </si>
+  <si>
+    <t>Jamnagar</t>
+  </si>
+  <si>
+    <t>Jamshedpur</t>
+  </si>
+  <si>
+    <t>Jharsuguda</t>
+  </si>
+  <si>
+    <t>Jodhpur</t>
+  </si>
+  <si>
+    <t>Jorhat</t>
+  </si>
+  <si>
+    <t>Kadapa</t>
+  </si>
+  <si>
+    <t>Kandla</t>
+  </si>
+  <si>
+    <t>Kangra</t>
+  </si>
+  <si>
+    <t>Kannur</t>
+  </si>
+  <si>
+    <t>Kanpur</t>
+  </si>
+  <si>
+    <t>Keshod</t>
+  </si>
+  <si>
+    <t>Khajuraho</t>
+  </si>
+  <si>
+    <t>Kochi</t>
+  </si>
+  <si>
+    <t>Kota</t>
+  </si>
+  <si>
+    <t>Kozhikode</t>
+  </si>
+  <si>
+    <t>Kullu</t>
+  </si>
+  <si>
+    <t>Kurnool</t>
+  </si>
+  <si>
+    <t>Kushinagar</t>
+  </si>
+  <si>
+    <t>Leh</t>
+  </si>
+  <si>
+    <t>Lilabari</t>
+  </si>
+  <si>
+    <t>Ludhiana</t>
+  </si>
+  <si>
+    <t>Madurai</t>
+  </si>
+  <si>
+    <t>Malda</t>
+  </si>
+  <si>
+    <t>Manali</t>
+  </si>
+  <si>
+    <t>Mangaluru</t>
+  </si>
+  <si>
+    <t>Mopa</t>
+  </si>
+  <si>
+    <t>Mysuru</t>
+  </si>
+  <si>
+    <t>Nagpur</t>
+  </si>
+  <si>
+    <t>Nanded</t>
+  </si>
+  <si>
+    <t>Nashik</t>
+  </si>
+  <si>
+    <t>Navi Mumbai</t>
+  </si>
+  <si>
+    <t>Pakyong</t>
+  </si>
+  <si>
+    <t>Palanpur</t>
+  </si>
+  <si>
+    <t>Pantnagar</t>
+  </si>
+  <si>
+    <t>Pasighat</t>
+  </si>
+  <si>
+    <t>Pathankot</t>
+  </si>
+  <si>
+    <t>Patna</t>
+  </si>
+  <si>
+    <t>Pondicherry</t>
+  </si>
+  <si>
+    <t>Porbandar</t>
+  </si>
+  <si>
+    <t>Port Blair</t>
+  </si>
+  <si>
+    <t>Prayagraj</t>
+  </si>
+  <si>
+    <t>Purnea</t>
+  </si>
+  <si>
+    <t>Puttaparthi</t>
+  </si>
+  <si>
+    <t>Raipur</t>
+  </si>
+  <si>
+    <t>Rajahmundry</t>
+  </si>
+  <si>
+    <t>Rajkot</t>
+  </si>
+  <si>
+    <t>Ranchi</t>
+  </si>
+  <si>
+    <t>Ratnagiri</t>
+  </si>
+  <si>
+    <t>Raxaul</t>
+  </si>
+  <si>
+    <t>Rourkela</t>
+  </si>
+  <si>
+    <t>Rupsi</t>
+  </si>
+  <si>
+    <t>Salem</t>
+  </si>
+  <si>
+    <t>Shillong</t>
+  </si>
+  <si>
+    <t>Shimla</t>
+  </si>
+  <si>
+    <t>Shirdi</t>
+  </si>
+  <si>
+    <t>Shivamogga</t>
+  </si>
+  <si>
+    <t>Silchar</t>
+  </si>
+  <si>
+    <t>Sindhudurg</t>
+  </si>
+  <si>
+    <t>Solapur</t>
+  </si>
+  <si>
+    <t>Sri Vijaya Puram</t>
+  </si>
+  <si>
+    <t>Srinagar</t>
+  </si>
+  <si>
+    <t>Surat</t>
+  </si>
+  <si>
+    <t>Surendranagar</t>
+  </si>
+  <si>
+    <t>Tezpur</t>
+  </si>
+  <si>
+    <t>Tezu</t>
+  </si>
+  <si>
+    <t>Thanjavur</t>
+  </si>
+  <si>
+    <t>Thiruvananthapuram</t>
+  </si>
+  <si>
+    <t>Tiruchirappalli</t>
+  </si>
+  <si>
+    <t>Tirupati</t>
+  </si>
+  <si>
+    <t>Tuticorin</t>
+  </si>
+  <si>
+    <t>Udaipur</t>
+  </si>
+  <si>
+    <t>Vadodara</t>
+  </si>
+  <si>
+    <t>Varanasi</t>
+  </si>
+  <si>
+    <t>Vellore</t>
+  </si>
+  <si>
+    <t>Vijayanagar</t>
+  </si>
+  <si>
+    <t>Vijayapura</t>
+  </si>
+  <si>
+    <t>Vijayawada</t>
+  </si>
+  <si>
+    <t>Visakhapatnam</t>
+  </si>
+  <si>
+    <t>Warangal</t>
+  </si>
+  <si>
+    <t>Bhogapuram</t>
+  </si>
+  <si>
+    <t>Junior Executive</t>
+  </si>
+  <si>
+    <t>Assistant Manager</t>
+  </si>
+  <si>
+    <t>Manager</t>
+  </si>
+  <si>
+    <t>Senior Manager</t>
+  </si>
+  <si>
+    <t>Assistant General Manager</t>
+  </si>
+  <si>
+    <t>Deputy General Manager</t>
+  </si>
+  <si>
+    <t>Joint General Manager</t>
+  </si>
+  <si>
+    <t>CNS</t>
+  </si>
+  <si>
+    <t>ATC</t>
+  </si>
+  <si>
+    <t>Electrical</t>
+  </si>
+  <si>
+    <t>Civil</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -48,81 +547,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -410,89 +851,736 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:A145"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Station</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Delhi</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Kolkata</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Ahmedabad</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Lucknow</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Jaipur</t>
-        </is>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A139" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A140" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A141" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A142" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A143" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A144" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A145" s="1" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -501,93 +1589,74 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.21875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Designation</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Designation 1</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Designation 2</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3">
         <v>2</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Designation 3</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4">
         <v>3</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Designation 4</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B5">
         <v>4</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Designation 5</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B6">
         <v>5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Designation 6</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>153</v>
+      </c>
+      <c r="B7">
         <v>6</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Designation 7</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B8">
         <v>7</v>
       </c>
     </row>
@@ -597,40 +1666,46 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Administration</t>
-        </is>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mutual_Transfer Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB2CF85-7676-472B-B556-6BF4FBFAA475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C934E1-01CB-48A2-A4E8-2AB09970F409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stations" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="164">
   <si>
     <t>Station</t>
   </si>
@@ -505,6 +505,15 @@
   </si>
   <si>
     <t>HR</t>
+  </si>
+  <si>
+    <t>Ooty</t>
+  </si>
+  <si>
+    <t>Bellary</t>
+  </si>
+  <si>
+    <t>Kolhapur</t>
   </si>
 </sst>
 </file>
@@ -852,7 +861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A145"/>
+  <dimension ref="A1:A148"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.44140625" customWidth="1"/>
@@ -944,642 +953,657 @@
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>6</v>
+      <c r="A18" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>147</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>61</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>65</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>81</v>
+        <v>163</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>82</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>2</v>
+        <v>92</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>101</v>
+        <v>161</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>7</v>
+        <v>106</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>111</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A146" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A147" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A148" s="1" t="s">
         <v>146</v>
       </c>
     </row>
